--- a/prisma/universities/University Track(Associate Degree)/Kyungbok University/1. 2027 GKS-U Available Departments(Kyungbok Univ.).xlsx
+++ b/prisma/universities/University Track(Associate Degree)/Kyungbok University/1. 2027 GKS-U Available Departments(Kyungbok Univ.).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NIIED\Desktop\전문학사\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\max\Desktop\projects\gks-universities\prisma\universities\University Track(Associate Degree)\Kyungbok University\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CB3D021-29C4-4F57-9BE3-676B554AED8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BBFA00-7C13-4E7B-AD15-2D252F707AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kyungbok University" sheetId="4" r:id="rId1"/>
@@ -31,9 +31,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -381,18 +378,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -444,7 +441,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -579,10 +576,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -600,6 +597,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -609,14 +609,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -637,9 +634,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -677,9 +674,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -712,26 +709,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -764,26 +744,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -962,51 +925,51 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.3"/>
   <cols>
-    <col min="1" max="1" width="6.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.15234375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.23046875" style="2" customWidth="1"/>
     <col min="3" max="3" width="13" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.15234375" style="2" customWidth="1"/>
     <col min="5" max="5" width="19" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="28.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.875" style="2" customWidth="1"/>
-    <col min="11" max="12" width="10.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.25" style="2" customWidth="1"/>
-    <col min="14" max="14" width="15.25" style="2" customWidth="1"/>
-    <col min="15" max="15" width="10.5" style="2" customWidth="1"/>
-    <col min="16" max="16" width="23.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.23046875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.765625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="28.3828125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.61328125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.84375" style="2" customWidth="1"/>
+    <col min="11" max="12" width="10.4609375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.23046875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="15.23046875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="10.4609375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="23.61328125" style="2" customWidth="1"/>
     <col min="17" max="17" width="16" style="2" customWidth="1"/>
-    <col min="18" max="18" width="36.625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="36.61328125" style="2" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:18" ht="41.25" customHeight="1" thickBot="1">
+      <c r="A1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="18"/>
     </row>
-    <row r="2" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="41.25" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1026,7 +989,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="1:18" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="60.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1082,9 +1045,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="35.15" customHeight="1">
       <c r="A4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>22</v>
@@ -1107,10 +1070,10 @@
       <c r="H4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="15" t="s">
         <v>8</v>
       </c>
       <c r="K4" s="10" t="s">
@@ -1136,9 +1099,9 @@
       </c>
       <c r="R4" s="4"/>
     </row>
-    <row r="5" spans="1:18" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="54.75" customHeight="1">
       <c r="A5" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>22</v>
@@ -1161,10 +1124,10 @@
       <c r="H5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="K5" s="10" t="s">
@@ -1192,9 +1155,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="35.15" customHeight="1">
       <c r="A6" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>22</v>
@@ -1217,10 +1180,10 @@
       <c r="H6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="15" t="s">
         <v>96</v>
       </c>
       <c r="K6" s="10" t="s">
@@ -1246,9 +1209,9 @@
       </c>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="35.15" customHeight="1">
       <c r="A7" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>22</v>
@@ -1271,10 +1234,10 @@
       <c r="H7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="15" t="s">
         <v>96</v>
       </c>
       <c r="K7" s="10" t="s">
@@ -1300,9 +1263,9 @@
       </c>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="35.15" customHeight="1">
       <c r="A8" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>22</v>
@@ -1325,10 +1288,10 @@
       <c r="H8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="15" t="s">
         <v>96</v>
       </c>
       <c r="K8" s="10" t="s">
@@ -1354,9 +1317,9 @@
       </c>
       <c r="R8" s="4"/>
     </row>
-    <row r="9" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="35.15" customHeight="1">
       <c r="A9" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>22</v>
@@ -1379,10 +1342,10 @@
       <c r="H9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="15" t="s">
         <v>96</v>
       </c>
       <c r="K9" s="10" t="s">
@@ -1408,9 +1371,9 @@
       </c>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="41.25" customHeight="1">
       <c r="A10" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>22</v>
@@ -1433,10 +1396,10 @@
       <c r="H10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="15" t="s">
         <v>96</v>
       </c>
       <c r="K10" s="10" t="s">
@@ -1464,9 +1427,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="35.15" customHeight="1">
       <c r="A11" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>22</v>
@@ -1489,10 +1452,10 @@
       <c r="H11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="15" t="s">
         <v>67</v>
       </c>
       <c r="K11" s="10" t="s">
@@ -1518,9 +1481,9 @@
       </c>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="35.15" customHeight="1">
       <c r="A12" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>22</v>
@@ -1543,10 +1506,10 @@
       <c r="H12" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="15" t="s">
         <v>66</v>
       </c>
       <c r="K12" s="10" t="s">
@@ -1572,9 +1535,9 @@
       </c>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="35.15" customHeight="1">
       <c r="A13" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>22</v>
@@ -1597,10 +1560,10 @@
       <c r="H13" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="J13" s="15" t="s">
         <v>66</v>
       </c>
       <c r="K13" s="10" t="s">
@@ -1626,9 +1589,9 @@
       </c>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="35.15" customHeight="1">
       <c r="A14" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>22</v>
@@ -1651,10 +1614,10 @@
       <c r="H14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J14" s="15" t="s">
         <v>66</v>
       </c>
       <c r="K14" s="10" t="s">
@@ -1680,9 +1643,9 @@
       </c>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="35.15" customHeight="1">
       <c r="A15" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>22</v>
@@ -1705,10 +1668,10 @@
       <c r="H15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="I15" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J15" s="15" t="s">
         <v>95</v>
       </c>
       <c r="K15" s="10" t="s">
@@ -1734,9 +1697,9 @@
       </c>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="35.15" customHeight="1">
       <c r="A16" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>22</v>
@@ -1759,10 +1722,10 @@
       <c r="H16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="18" t="s">
+      <c r="I16" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J16" s="18" t="s">
+      <c r="J16" s="15" t="s">
         <v>95</v>
       </c>
       <c r="K16" s="10" t="s">
@@ -1788,9 +1751,9 @@
       </c>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="35.15" customHeight="1">
       <c r="A17" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>22</v>
@@ -1813,10 +1776,10 @@
       <c r="H17" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J17" s="18" t="s">
+      <c r="J17" s="15" t="s">
         <v>95</v>
       </c>
       <c r="K17" s="10" t="s">
@@ -1847,15 +1810,12 @@
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I17 K5:K17" xr:uid="{00000000-0002-0000-0000-000001000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K17 I4:J17" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L17" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"2,3,4,5,6"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J17" xr:uid="{1A9E1F72-CF61-4185-8C7D-4628FB48B380}">
-      <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
